--- a/server/data/xlsx/DungeonData.xlsx
+++ b/server/data/xlsx/DungeonData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,21 @@
           <t>MonsterIds[]</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>DungeonType</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>TimeLimitSeconds</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>RespawnDelaySeconds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -569,6 +584,21 @@
           <t>int</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>DungeonType</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -644,6 +674,21 @@
       <c r="O3" t="inlineStr">
         <is>
           <t>몬스터ID_10</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>던전타입</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>제한시간(초)</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>리스폰딜레이(초)</t>
         </is>
       </c>
     </row>
@@ -697,6 +742,15 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>300</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -748,6 +802,15 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>300</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -798,6 +861,75 @@
       </c>
       <c r="O6" t="n">
         <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>600</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Goblin Rush</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>끝없이 밀려오는 고블린 - 제한시간 생존 던전</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>120</v>
+      </c>
+      <c r="R7" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
